--- a/data/Wondrous_Magic_script.xlsx
+++ b/data/Wondrous_Magic_script.xlsx
@@ -11,17 +11,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Script" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item names" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Descriptions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Title screen" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name entry" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intro crawl" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control codes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monster names" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Title screen" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name entry" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intro crawl" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control codes" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Script'!$A$1:$J$921</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Glossary'!$A$1:$D$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Questions'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Glossary'!$A$1:$D$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Questions'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +66,12 @@
     <font>
       <name val="Courier New"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -112,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +183,10 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -813,6 +824,379 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>What I did / what I need</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>0x09A47F, 0x09AB09</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Zaifon: ally or betrayer?</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Rinkle first accuses Zaifon of feeding them to a dragon; Zaifon is then a straightforward ally and dies offscreen. I have kept Rinkle’s accusation hot and Zaifon’s replies calm, which works either way, but "master of all mages" is an honorific choice that should track the eventual reveal.</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>0x09F6AC, 0x09FADD</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>レ・リュース rendered "Le Ryus"</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Forest city of the elves. Could equally be Le Ruse, Le Luce, Le Reuse. Chose a neutral transliteration; the French-looking レ argues for "Le X".</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>0x099E3E</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>フェイド rendered "Fade"</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Mountain range. "Feid" is also defensible; "Fade" reads as an English word, which may or may not be wanted.</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>0x09F465, 0x09E8D6</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>ドラゴノーク rendered "Dragonork"</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Overworld mount given by Cope. Not present in script_a NAMES, so there is no established rendering to match. Compare Dragonoim.</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>0x0A0F82, 0x0A41A4</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>ロイド・フォン rendered "Loyd Von"</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Ivuas’s perfected form and, per the library, the god of the Will. Lloyd Fon / Royd Von also possible.</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>0x0A5199</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>イリオン・マオ・クラップ rendered "Ilion Mao Clap"</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>"Clap" is an unfortunate English word. Klapp / Crap / Krapp all fit the kana. Only appears in one library book.</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>throughout</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>意識 rendered "the Will"</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Chose "the Will" / "the Evil Will" / "the War of Wills" for consistency across 意識, 悪の意識 and 意識の争い. "Consciousness" is more literal but unusable at 28 columns.</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>throughout</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>&lt;EE9&gt; left as a token, not converted to "..."</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>It is the ─ dash glyph, used both as a window rule and as a trailing-off dash in dialogue. Kept in place, matching the existing 0x098CDB translation. The house rule about ASCII ellipses applies to …, which is separate.</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>0x0A16F1 and 23 others</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>メッセージNNN placeholders</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Debug strings left in the retail ROM. Rendered literally as MessageNNN so they stay obviously non-content. Say the word and I will leave them untranslated instead.</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>0x099C1B</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Fredia is addressed as にいさん</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>The heroine calls him "brother" while looking into the Bloodstone, well before the reveal at 0x0A06C8. Translated straight as "Brother", which preserves the foreshadowing without spoiling it.</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>0x09E013</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Batica’s 女はイヤだよ</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>She refuses the heroine’s offer to tell her stories because she dislikes women, and demands Fredia instead. Rendered plainly; it reads oddly in English but the plot depends on it (Fredia is separated from the party).</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>0x09A0EB, 0x09E96A</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>町長 vs ドワーフの長</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Both are village heads. Used "Elder" for human towns and "Dwarf Elder" for Zev so the nameplates stay distinguishable.</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>0x0A2D68</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Hob and Babam dialects</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Hob speaks ずら/だべ (rustic), Babam speaks Kansai. Rendered as light rustic English ("I ain’t", "summat") and brisk plain English respectively. Happy to push either further.</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>0x0A4D37</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>キャビット rendered "cabbit"</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>The talking animal of rumour in the Book of Ilias. Almost certainly Charl, given 0x0A3F72 where Charl speaks. Lower-cased as a species.</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>0x0A45E1, 0x0A4636</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Currency conversion tables left unchanged</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Pure numerals and &lt;S39&gt;/&lt;S3A&gt;/&lt;EF0&gt; tokens - nothing to translate. Column alignment is load-bearing, so the spacing is byte-for-byte identical to the Japanese.</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -12977,7 +13361,7 @@
       </c>
       <c r="H239" s="22" t="inlineStr">
         <is>
-          <t>Hood</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="I239" s="20">
@@ -13028,7 +13412,7 @@
       </c>
       <c r="H240" s="22" t="inlineStr">
         <is>
-          <t>Hood
+          <t>Food
  Restores 60% of health,
  once.</t>
         </is>
@@ -56029,7 +56413,7 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>Hood</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -58873,6 +59257,1571 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>ROM</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>Chars</t>
+        </is>
+      </c>
+      <c r="G1" s="24" t="inlineStr">
+        <is>
+          <t>12 ASCII characters maximum - six 16x16 cells, two half-width letters each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>$153000</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
+        <is>
+          <t>バット</t>
+        </is>
+      </c>
+      <c r="D2" s="26" t="inlineStr">
+        <is>
+          <t>Bat</t>
+        </is>
+      </c>
+      <c r="E2" s="2">
+        <f>LEN(D2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>$15300C</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>ビィ</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Bee</t>
+        </is>
+      </c>
+      <c r="E3" s="2">
+        <f>LEN(D3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>$153018</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>クイーンビィ</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>Queen Bee</t>
+        </is>
+      </c>
+      <c r="E4" s="2">
+        <f>LEN(D4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>$153024</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>トレント</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Treant</t>
+        </is>
+      </c>
+      <c r="E5" s="2">
+        <f>LEN(D5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>$153030</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>ワービースト</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Werebeast</t>
+        </is>
+      </c>
+      <c r="E6" s="2">
+        <f>LEN(D6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>$15303C</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>ブレイド</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Blade</t>
+        </is>
+      </c>
+      <c r="E7" s="2">
+        <f>LEN(D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>$153048</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>ハーフゾンビ</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Half Zombie</t>
+        </is>
+      </c>
+      <c r="E8" s="2">
+        <f>LEN(D8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>$153054</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>リザーダ</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Lizarder</t>
+        </is>
+      </c>
+      <c r="E9" s="2">
+        <f>LEN(D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>$153060</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>プラント</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="E10" s="2">
+        <f>LEN(D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>$15306C</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>プチドラゴン</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Petit Dragon</t>
+        </is>
+      </c>
+      <c r="E11" s="2">
+        <f>LEN(D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>$153078</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>ドラゴニア</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Dragonia</t>
+        </is>
+      </c>
+      <c r="E12" s="2">
+        <f>LEN(D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>$153084</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>マザーデモン</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Mother Demon</t>
+        </is>
+      </c>
+      <c r="E13" s="2">
+        <f>LEN(D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>$153090</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>ウィスプ</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Wisp</t>
+        </is>
+      </c>
+      <c r="E14" s="2">
+        <f>LEN(D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>$15309C</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>ハーピィ</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Harpy</t>
+        </is>
+      </c>
+      <c r="E15" s="2">
+        <f>LEN(D15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>$1530A8</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>バシリスク</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Basilisk</t>
+        </is>
+      </c>
+      <c r="E16" s="2">
+        <f>LEN(D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>$1530B4</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>トロール</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Troll</t>
+        </is>
+      </c>
+      <c r="E17" s="2">
+        <f>LEN(D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>$1530C0</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>グリフォン</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>Griffon</t>
+        </is>
+      </c>
+      <c r="E18" s="2">
+        <f>LEN(D18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>$1530CC</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>トルネード</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>Tornado</t>
+        </is>
+      </c>
+      <c r="E19" s="2">
+        <f>LEN(D19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>$1530D8</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>ワーム</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Worm</t>
+        </is>
+      </c>
+      <c r="E20" s="2">
+        <f>LEN(D20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>$1530E4</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>コカトリス</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Cockatrice</t>
+        </is>
+      </c>
+      <c r="E21" s="2">
+        <f>LEN(D21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>$1530F0</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>ダストマン</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>Dust Man</t>
+        </is>
+      </c>
+      <c r="E22" s="2">
+        <f>LEN(D22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>$1530FC</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>フルゾンビ</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Full Zombie</t>
+        </is>
+      </c>
+      <c r="E23" s="2">
+        <f>LEN(D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>$153108</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>スカリオット</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>Scariot</t>
+        </is>
+      </c>
+      <c r="E24" s="2">
+        <f>LEN(D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>$153114</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>スピリット</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Spirit</t>
+        </is>
+      </c>
+      <c r="E25" s="2">
+        <f>LEN(D25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>$153120</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>ヴァンパイア</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Vampire</t>
+        </is>
+      </c>
+      <c r="E26" s="2">
+        <f>LEN(D26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>$15312C</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>ハイデーモン</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>High Demon</t>
+        </is>
+      </c>
+      <c r="E27" s="2">
+        <f>LEN(D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>$153138</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>ゴースト</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Ghost</t>
+        </is>
+      </c>
+      <c r="E28" s="2">
+        <f>LEN(D28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>$153144</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>フレシュマン</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Fleshman</t>
+        </is>
+      </c>
+      <c r="E29" s="2">
+        <f>LEN(D29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>$153150</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>ダークマギ</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Dark Magi</t>
+        </is>
+      </c>
+      <c r="E30" s="2">
+        <f>LEN(D30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>$15315C</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>スケルトン</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>Skeleton</t>
+        </is>
+      </c>
+      <c r="E31" s="2">
+        <f>LEN(D31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>$153168</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>デュラハン</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>Dullahan</t>
+        </is>
+      </c>
+      <c r="E32" s="2">
+        <f>LEN(D32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>$153174</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>ラミア</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Lamia</t>
+        </is>
+      </c>
+      <c r="E33" s="2">
+        <f>LEN(D33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>$153180</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>ストンゴレム</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Stone Golem</t>
+        </is>
+      </c>
+      <c r="E34" s="2">
+        <f>LEN(D34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>$15318C</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>キングワーム</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>King Worm</t>
+        </is>
+      </c>
+      <c r="E35" s="2">
+        <f>LEN(D35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>$153198</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="inlineStr">
+        <is>
+          <t>ダストゴレム</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>Dust Golem</t>
+        </is>
+      </c>
+      <c r="E36" s="2">
+        <f>LEN(D36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>$1531A4</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>デビルマギ</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>Devil Magi</t>
+        </is>
+      </c>
+      <c r="E37" s="2">
+        <f>LEN(D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>$1531B0</t>
+        </is>
+      </c>
+      <c r="C38" s="25" t="inlineStr">
+        <is>
+          <t>ドップラー</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>Doppler</t>
+        </is>
+      </c>
+      <c r="E38" s="2">
+        <f>LEN(D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>$1531BC</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>サイクロプス</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>Cyclops</t>
+        </is>
+      </c>
+      <c r="E39" s="2">
+        <f>LEN(D39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>$1531C8</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="inlineStr">
+        <is>
+          <t>エビルナイト</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>Evil Knight</t>
+        </is>
+      </c>
+      <c r="E40" s="2">
+        <f>LEN(D40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>$1531D4</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>アクアマスク</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>Aqua Mask</t>
+        </is>
+      </c>
+      <c r="E41" s="2">
+        <f>LEN(D41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>$1531E0</t>
+        </is>
+      </c>
+      <c r="C42" s="25" t="inlineStr">
+        <is>
+          <t>クリアシェル</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>Clear Shell</t>
+        </is>
+      </c>
+      <c r="E42" s="2">
+        <f>LEN(D42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>$1531EC</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>クラウド</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E43" s="2">
+        <f>LEN(D43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>$1531F8</t>
+        </is>
+      </c>
+      <c r="C44" s="25" t="inlineStr">
+        <is>
+          <t>アルラウネ</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>Alraune</t>
+        </is>
+      </c>
+      <c r="E44" s="2">
+        <f>LEN(D44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>$153204</t>
+        </is>
+      </c>
+      <c r="C45" s="25" t="inlineStr">
+        <is>
+          <t>バンシィ</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>Banshee</t>
+        </is>
+      </c>
+      <c r="E45" s="2">
+        <f>LEN(D45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>$153210</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>キメラ</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>Chimera</t>
+        </is>
+      </c>
+      <c r="E46" s="2">
+        <f>LEN(D46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>$15321C</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="inlineStr">
+        <is>
+          <t>ローパー</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>Roper</t>
+        </is>
+      </c>
+      <c r="E47" s="2">
+        <f>LEN(D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>$153228</t>
+        </is>
+      </c>
+      <c r="C48" s="25" t="inlineStr">
+        <is>
+          <t>マガット</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>Maggot</t>
+        </is>
+      </c>
+      <c r="E48" s="2">
+        <f>LEN(D48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>$153234</t>
+        </is>
+      </c>
+      <c r="C49" s="25" t="inlineStr">
+        <is>
+          <t>ネクロマンサ</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>Necromancer</t>
+        </is>
+      </c>
+      <c r="E49" s="2">
+        <f>LEN(D49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>$153240</t>
+        </is>
+      </c>
+      <c r="C50" s="25" t="inlineStr">
+        <is>
+          <t>ワイヴァーン</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
+        <is>
+          <t>Wyvern</t>
+        </is>
+      </c>
+      <c r="E50" s="2">
+        <f>LEN(D50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>$15324C</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="inlineStr">
+        <is>
+          <t>デス</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="inlineStr">
+        <is>
+          <t>Death</t>
+        </is>
+      </c>
+      <c r="E51" s="2">
+        <f>LEN(D51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>$153258</t>
+        </is>
+      </c>
+      <c r="C52" s="25" t="inlineStr">
+        <is>
+          <t>ドナルド</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr">
+        <is>
+          <t>Donald</t>
+        </is>
+      </c>
+      <c r="E52" s="2">
+        <f>LEN(D52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>$153264</t>
+        </is>
+      </c>
+      <c r="C53" s="25" t="inlineStr">
+        <is>
+          <t>ストーカー</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="inlineStr">
+        <is>
+          <t>Stalker</t>
+        </is>
+      </c>
+      <c r="E53" s="2">
+        <f>LEN(D53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>$153270</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="inlineStr">
+        <is>
+          <t>フリジット</t>
+        </is>
+      </c>
+      <c r="D54" s="26" t="inlineStr">
+        <is>
+          <t>Frigid</t>
+        </is>
+      </c>
+      <c r="E54" s="2">
+        <f>LEN(D54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>$15327C</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="inlineStr">
+        <is>
+          <t>ドラゴゾンビ</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="inlineStr">
+        <is>
+          <t>Dragozombie</t>
+        </is>
+      </c>
+      <c r="E55" s="2">
+        <f>LEN(D55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>$153288</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="inlineStr">
+        <is>
+          <t>シェルスコ</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>Shell Scorp</t>
+        </is>
+      </c>
+      <c r="E56" s="2">
+        <f>LEN(D56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>$153294</t>
+        </is>
+      </c>
+      <c r="C57" s="25" t="inlineStr">
+        <is>
+          <t>ストーカー</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
+        <is>
+          <t>Stalker</t>
+        </is>
+      </c>
+      <c r="E57" s="2">
+        <f>LEN(D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>$1532A0</t>
+        </is>
+      </c>
+      <c r="C58" s="25" t="inlineStr">
+        <is>
+          <t>クラーケン</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="E58" s="2">
+        <f>LEN(D58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>$1532AC</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
+        <is>
+          <t>イリオン</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>Ilion</t>
+        </is>
+      </c>
+      <c r="E59" s="2">
+        <f>LEN(D59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>$1532B8</t>
+        </is>
+      </c>
+      <c r="C60" s="25" t="inlineStr">
+        <is>
+          <t>イヴァス</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="inlineStr">
+        <is>
+          <t>Ivas</t>
+        </is>
+      </c>
+      <c r="E60" s="2">
+        <f>LEN(D60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>$1532C4</t>
+        </is>
+      </c>
+      <c r="C61" s="25" t="inlineStr">
+        <is>
+          <t>ロイドフォン</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
+        <is>
+          <t>Loydphon</t>
+        </is>
+      </c>
+      <c r="E61" s="2">
+        <f>LEN(D61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>$1532D0</t>
+        </is>
+      </c>
+      <c r="C62" s="25" t="inlineStr">
+        <is>
+          <t>シェルスコ</t>
+        </is>
+      </c>
+      <c r="D62" s="26" t="inlineStr">
+        <is>
+          <t>Shell Scorp</t>
+        </is>
+      </c>
+      <c r="E62" s="2">
+        <f>LEN(D62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>$1532DC</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>クラーケン</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="E63" s="2">
+        <f>LEN(D63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>$1532E8</t>
+        </is>
+      </c>
+      <c r="C64" s="25" t="inlineStr">
+        <is>
+          <t>ロイドフォン</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="inlineStr">
+        <is>
+          <t>Loydphon</t>
+        </is>
+      </c>
+      <c r="E64" s="2">
+        <f>LEN(D64)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -59029,7 +60978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -59165,7 +61114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -59855,7 +61804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -62052,377 +64001,4 @@
   <autoFilter ref="A1:D103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="74" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Where</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>What I did / what I need</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>0x09A47F, 0x09AB09</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Zaifon: ally or betrayer?</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>Rinkle first accuses Zaifon of feeding them to a dragon; Zaifon is then a straightforward ally and dies offscreen. I have kept Rinkle’s accusation hot and Zaifon’s replies calm, which works either way, but "master of all mages" is an honorific choice that should track the eventual reveal.</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>0x09F6AC, 0x09FADD</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>レ・リュース rendered "Le Ryus"</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Forest city of the elves. Could equally be Le Ruse, Le Luce, Le Reuse. Chose a neutral transliteration; the French-looking レ argues for "Le X".</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>0x099E3E</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>フェイド rendered "Fade"</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Mountain range. "Feid" is also defensible; "Fade" reads as an English word, which may or may not be wanted.</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>0x09F465, 0x09E8D6</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>ドラゴノーク rendered "Dragonork"</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Overworld mount given by Cope. Not present in script_a NAMES, so there is no established rendering to match. Compare Dragonoim.</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>0x0A0F82, 0x0A41A4</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>ロイド・フォン rendered "Loyd Von"</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Ivuas’s perfected form and, per the library, the god of the Will. Lloyd Fon / Royd Von also possible.</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>0x0A5199</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>イリオン・マオ・クラップ rendered "Ilion Mao Clap"</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>"Clap" is an unfortunate English word. Klapp / Crap / Krapp all fit the kana. Only appears in one library book.</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>throughout</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>意識 rendered "the Will"</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Chose "the Will" / "the Evil Will" / "the War of Wills" for consistency across 意識, 悪の意識 and 意識の争い. "Consciousness" is more literal but unusable at 28 columns.</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>throughout</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>&lt;EE9&gt; left as a token, not converted to "..."</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>It is the ─ dash glyph, used both as a window rule and as a trailing-off dash in dialogue. Kept in place, matching the existing 0x098CDB translation. The house rule about ASCII ellipses applies to …, which is separate.</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>resolved</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>0x0A16F1 and 23 others</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>メッセージNNN placeholders</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Debug strings left in the retail ROM. Rendered literally as MessageNNN so they stay obviously non-content. Say the word and I will leave them untranslated instead.</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>0x099C1B</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Fredia is addressed as にいさん</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>The heroine calls him "brother" while looking into the Bloodstone, well before the reveal at 0x0A06C8. Translated straight as "Brother", which preserves the foreshadowing without spoiling it.</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>resolved</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>0x09E013</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Batica’s 女はイヤだよ</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>She refuses the heroine’s offer to tell her stories because she dislikes women, and demands Fredia instead. Rendered plainly; it reads oddly in English but the plot depends on it (Fredia is separated from the party).</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>0x09A0EB, 0x09E96A</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>町長 vs ドワーフの長</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Both are village heads. Used "Elder" for human towns and "Dwarf Elder" for Zev so the nameplates stay distinguishable.</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>resolved</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>0x0A2D68</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Hob and Babam dialects</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Hob speaks ずら/だべ (rustic), Babam speaks Kansai. Rendered as light rustic English ("I ain’t", "summat") and brisk plain English respectively. Happy to push either further.</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>0x0A4D37</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>キャビット rendered "cabbit"</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>The talking animal of rumour in the Book of Ilias. Almost certainly Charl, given 0x0A3F72 where Charl speaks. Lower-cased as a species.</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>0x0A45E1, 0x0A4636</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Currency conversion tables left unchanged</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Pure numerals and &lt;S39&gt;/&lt;S3A&gt;/&lt;EF0&gt; tokens - nothing to translate. Column alignment is load-bearing, so the spacing is byte-for-byte identical to the Japanese.</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>resolved</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D16"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>